--- a/VerveStacks_POL_grids_kan10/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan10/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCC4C841-AFFC-47DE-9538-453E3DD06BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{57F38573-2CAC-4878-A83B-98C2581D2036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D96A4729-5C45-4535-A710-EB8A32C74B0F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CE1EAFDD-A182-4CB6-A5D1-4EC30B877A2B}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3736,7 +3736,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C7ACB19-D5CB-4A38-8039-16F0E1DC8594}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1997876B-CD45-48D2-AF2E-737BC57B63EA}">
   <dimension ref="B9:V189"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -14914,7 +14914,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FED935F-910F-449C-BBE8-129BD49FBF5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE687857-0E5F-41E3-872B-C5EF9C346D57}">
   <dimension ref="B9:W151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -22461,7 +22461,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4548A288-7438-4BBC-8A6B-665AE6417048}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71037ED6-9483-4542-95C6-293C2B6A83B4}">
   <dimension ref="B9:W381"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -35158,7 +35158,7 @@
         <v>15</v>
       </c>
       <c r="S227" t="s">
-        <v>350</v>
+        <v>553</v>
       </c>
       <c r="T227" t="s">
         <v>339</v>
@@ -35220,7 +35220,7 @@
         <v>15</v>
       </c>
       <c r="S228" t="s">
-        <v>553</v>
+        <v>350</v>
       </c>
       <c r="T228" t="s">
         <v>339</v>
@@ -35778,7 +35778,7 @@
         <v>15</v>
       </c>
       <c r="S237" t="s">
-        <v>350</v>
+        <v>553</v>
       </c>
       <c r="T237" t="s">
         <v>339</v>
@@ -35840,7 +35840,7 @@
         <v>15</v>
       </c>
       <c r="S238" t="s">
-        <v>553</v>
+        <v>350</v>
       </c>
       <c r="T238" t="s">
         <v>339</v>
@@ -37142,7 +37142,7 @@
         <v>15</v>
       </c>
       <c r="S259" t="s">
-        <v>553</v>
+        <v>350</v>
       </c>
       <c r="T259" t="s">
         <v>339</v>
@@ -37204,7 +37204,7 @@
         <v>15</v>
       </c>
       <c r="S260" t="s">
-        <v>350</v>
+        <v>553</v>
       </c>
       <c r="T260" t="s">
         <v>339</v>
@@ -37452,7 +37452,7 @@
         <v>15</v>
       </c>
       <c r="S264" t="s">
-        <v>553</v>
+        <v>350</v>
       </c>
       <c r="T264" t="s">
         <v>339</v>
@@ -37514,7 +37514,7 @@
         <v>15</v>
       </c>
       <c r="S265" t="s">
-        <v>350</v>
+        <v>553</v>
       </c>
       <c r="T265" t="s">
         <v>339</v>
@@ -42132,7 +42132,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BAAA0E5-E08B-4D1D-BC86-7E9E50767EA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3E2810E-BCA7-4F34-9022-D716E83924E8}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
